--- a/outputs/bwlp_fv_report.xlsx
+++ b/outputs/bwlp_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.52</v>
+        <v>19.45</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>124605.4070891389</v>
+        <v>146333.9631689615</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.373436325507408</v>
+        <v>2.787313584170696</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/bwlp_fv_report.xlsx
+++ b/outputs/bwlp_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.45</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>146333.9631689615</v>
+        <v>161520.5883860418</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.787313584170696</v>
+        <v>3.076582635924606</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/bwlp_fv_report.xlsx
+++ b/outputs/bwlp_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.1</v>
+        <v>21.1556</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>161520.5883860418</v>
+        <v>186183.6677385802</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.076582635924606</v>
+        <v>3.546355575972957</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/bwlp_fv_report.xlsx
+++ b/outputs/bwlp_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.1556</v>
+        <v>20.3488</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>186183.6677385802</v>
+        <v>167333.5612383643</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.546355575972957</v>
+        <v>3.187305928349796</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/bwlp_fv_report.xlsx
+++ b/outputs/bwlp_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.3488</v>
+        <v>21.1029</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>167333.5612383643</v>
+        <v>184952.3828940571</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.187305928349796</v>
+        <v>3.522902531315373</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/bwlp_fv_report.xlsx
+++ b/outputs/bwlp_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.1029</v>
+        <v>21.9952</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>184952.3828940571</v>
+        <v>205800.114711289</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.522902531315373</v>
+        <v>3.920002184976934</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/bwlp_fv_report.xlsx
+++ b/outputs/bwlp_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.9952</v>
+        <v>22.7028</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>205800.114711289</v>
+        <v>222332.5085629906</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.920002184976934</v>
+        <v>4.234904925009344</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/bwlp_fv_report.xlsx
+++ b/outputs/bwlp_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.7028</v>
+        <v>21.6026</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>222332.5085629906</v>
+        <v>196627.3930801724</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.234904925009344</v>
+        <v>3.745283677717571</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/bwlp_fv_report.xlsx
+++ b/outputs/bwlp_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.6026</v>
+        <v>22.0806</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>196627.3930801724</v>
+        <v>207795.4036244254</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.745283677717571</v>
+        <v>3.958007688084293</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/bwlp_fv_report.xlsx
+++ b/outputs/bwlp_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.0806</v>
+        <v>22.7519</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>207795.4036244254</v>
+        <v>223479.6828678499</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.958007688084293</v>
+        <v>4.256755864149522</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/bwlp_fv_report.xlsx
+++ b/outputs/bwlp_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.7519</v>
+        <v>25.0838</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>223479.6828678499</v>
+        <v>277962.2849350956</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.256755864149522</v>
+        <v>5.294519713049439</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/bwlp_fv_report.xlsx
+++ b/outputs/bwlp_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.0838</v>
+        <v>24.0493</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>277962.2849350956</v>
+        <v>253792.1868011423</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.294519713049439</v>
+        <v>4.83413689145033</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/bwlp_fv_report.xlsx
+++ b/outputs/bwlp_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.0493</v>
+        <v>24.0503</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>253792.1868011423</v>
+        <v>253815.5508399378</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.83413689145033</v>
+        <v>4.834581920760719</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/bwlp_fv_report.xlsx
+++ b/outputs/bwlp_fv_report.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.43382950866348</v>
+        <v>15.47827737877757</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.803546906698</v>
+        <v>15.83390491491853</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.57115557991628</v>
+        <v>14.64847979444869</v>
       </c>
     </row>
     <row r="9">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>253815.5508399378</v>
+        <v>252777.0690782146</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.834581920760719</v>
+        <v>4.814801315775515</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3046.357152221594</v>
+        <v>2992.11094109639</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>273.076</v>
+        <v>303.856</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>176.607</v>
+        <v>256.783</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-763.923</v>
+        <v>-814.248</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-133.908</v>
+        <v>-118.384</v>
       </c>
     </row>
     <row r="7">
@@ -702,7 +702,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>2399.209152221594</v>
+        <v>2403.81794109639</v>
       </c>
     </row>
     <row r="10">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15.803546906698</v>
+        <v>15.83390491491853</v>
       </c>
     </row>
     <row r="12">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15.803546906698</v>
+        <v>15.83390491491853</v>
       </c>
     </row>
     <row r="13">
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.7593195399849</v>
+        <v>13.85710903858476</v>
       </c>
       <c r="F11" t="n">
-        <v>10.87978352648276</v>
+        <v>10.95710774101517</v>
       </c>
     </row>
     <row r="12">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14.57115557991628</v>
+        <v>14.64847979444869</v>
       </c>
     </row>
     <row r="13">
@@ -1079,19 +1079,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.16006935487133</v>
+        <v>11.26829505730265</v>
       </c>
       <c r="C2" t="n">
-        <v>12.95989298065784</v>
+        <v>13.03622976693055</v>
       </c>
       <c r="D2" t="n">
-        <v>14.75971660644437</v>
+        <v>14.80416447655846</v>
       </c>
       <c r="E2" t="n">
-        <v>16.5595402322309</v>
+        <v>16.57209918618637</v>
       </c>
       <c r="F2" t="n">
-        <v>18.35936385801741</v>
+        <v>18.34003389581427</v>
       </c>
     </row>
     <row r="3">
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.49712580598088</v>
+        <v>11.60535150841221</v>
       </c>
       <c r="C3" t="n">
-        <v>13.2969494317674</v>
+        <v>13.3732862180401</v>
       </c>
       <c r="D3" t="n">
-        <v>15.09677305755393</v>
+        <v>15.14122092766802</v>
       </c>
       <c r="E3" t="n">
-        <v>16.89659668334046</v>
+        <v>16.90915563729593</v>
       </c>
       <c r="F3" t="n">
-        <v>18.69642030912696</v>
+        <v>18.67709034692383</v>
       </c>
     </row>
     <row r="4">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.83418225709044</v>
+        <v>11.94240795952176</v>
       </c>
       <c r="C4" t="n">
-        <v>13.63400588287696</v>
+        <v>13.71034266914966</v>
       </c>
       <c r="D4" t="n">
-        <v>15.43382950866348</v>
+        <v>15.47827737877757</v>
       </c>
       <c r="E4" t="n">
-        <v>17.23365313445002</v>
+        <v>17.24621208840549</v>
       </c>
       <c r="F4" t="n">
-        <v>19.03347676023652</v>
+        <v>19.01414679803339</v>
       </c>
     </row>
     <row r="5">
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.1712387082</v>
+        <v>12.27946441063132</v>
       </c>
       <c r="C5" t="n">
-        <v>13.97106233398651</v>
+        <v>14.04739912025922</v>
       </c>
       <c r="D5" t="n">
-        <v>15.77088595977304</v>
+        <v>15.81533382988713</v>
       </c>
       <c r="E5" t="n">
-        <v>17.57070958555957</v>
+        <v>17.58326853951505</v>
       </c>
       <c r="F5" t="n">
-        <v>19.37053321134608</v>
+        <v>19.35120324914294</v>
       </c>
     </row>
     <row r="6">
@@ -1167,19 +1167,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.50829515930955</v>
+        <v>12.61652086174088</v>
       </c>
       <c r="C6" t="n">
-        <v>14.30811878509607</v>
+        <v>14.38445557136878</v>
       </c>
       <c r="D6" t="n">
-        <v>16.1079424108826</v>
+        <v>16.15239028099669</v>
       </c>
       <c r="E6" t="n">
-        <v>17.90776603666913</v>
+        <v>17.9203249906246</v>
       </c>
       <c r="F6" t="n">
-        <v>19.70758966245564</v>
+        <v>19.6882597002525</v>
       </c>
     </row>
   </sheetData>
@@ -1217,7 +1217,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.44</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="3">
@@ -1225,7 +1225,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>15.47</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="4">
@@ -1233,7 +1233,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>15.48</v>
+        <v>15.52</v>
       </c>
     </row>
   </sheetData>
